--- a/database/seeders/data/07_AMENIDADES_Y_CLASES.xlsx
+++ b/database/seeders/data/07_AMENIDADES_Y_CLASES.xlsx
@@ -2,17 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AMENIDADES" sheetId="1" r:id="R54195eea078f4c24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HORARIOS AMENIDADES" sheetId="2" r:id="R3f0ddb735aba4520"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RECURSOS" sheetId="3" r:id="R4248362de0e7469e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UBICACIONES RECURSOS" sheetId="4" r:id="R26a83d2b68b24356"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERIODOS BLOQUEADOS" sheetId="5" r:id="R782ab4a679c54406"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESPECIALIDADES" sheetId="6" r:id="R45d5d05557594e79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENTRENADORES" sheetId="7" r:id="R6d12e27163aa4ece"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESPECIALIDADES ENTRENADOR" sheetId="8" r:id="R92be5e45aa8e477f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DISPONIBILIDAD ENTRENADORES" sheetId="9" r:id="R9197898affe649f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HORARIOS DE CLASES" sheetId="10" r:id="R3d15d96bb74b440e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSCRIPCIONES A CLASES" sheetId="11" r:id="R47b21b406f6e4208"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AMENIDADES" sheetId="1" r:id="Rd2c9ecf3617c40a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HORARIOS AMENIDADES" sheetId="2" r:id="Rae4c9c0a146f4502"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RECURSOS" sheetId="3" r:id="Rfa9228c0020d4ec5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UBICACIONES RECURSOS" sheetId="4" r:id="R01f7e4e771e64ae0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERIODOS BLOQUEADOS" sheetId="5" r:id="R2f73fc9d13374aee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESPECIALIDADES" sheetId="6" r:id="R412b287f80d0447f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENTRENADORES" sheetId="7" r:id="R0f19147aa973452a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESPECIALIDADES ENTRENADOR" sheetId="8" r:id="R5c2fa2d8ace44378"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DISPONIBILIDAD ENTRENADORES" sheetId="9" r:id="Rd0e80420011741d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HORARIOS DE CLASES" sheetId="10" r:id="R3f43175bd0d14f50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSCRIPCIONES A CLASES" sheetId="11" r:id="R4693e4ea892f4bf5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="12" r:id="R4304fe2dd4934e3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EJEMPLOS" sheetId="13" r:id="Rd01d4568829545a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +25,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:numFmts count="2">
+    <x:numFmt numFmtId="200" formatCode="&quot;$&quot;#,##0.00"/>
+    <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd hh:mm"/>
+  </x:numFmts>
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -39,8 +45,47 @@
       <x:color rgb="FF222222"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFC0392B"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF2980B9"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1E8449"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="18">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -52,8 +97,83 @@
         <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC0392B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2980B9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1A252F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFADBD8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD6EAF8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD5F5E3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEBF5FB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1A252F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC0392B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2980B9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEBF5FB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1A252F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC0392B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2980B9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEBF5FB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -69,11 +189,25 @@
         <x:color rgb="FFFFFFFF"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="103">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -90,6 +224,198 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -307,28 +633,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>NOMBRE DE LA AMENIDAD</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="12" t="str">
         <x:v>DESCRIPCIÓN</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>TIPO DE RESERVACIÓN</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="12" t="str">
         <x:v>ACTIVA</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="12" t="str">
         <x:v>NOMBRE O RUTA DEL ÍCONO</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="12" t="str">
         <x:v>NOMBRE O RUTA DE LA IMAGEN</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="12" t="str">
         <x:v>NOMBRE O RUTA DEL REGLAMENTO</x:v>
       </x:c>
     </x:row>
@@ -2350,43 +2676,43 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>NOMBRE DE LA CLASE</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="12" t="str">
         <x:v>TIPO DE CLASE</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="10" t="str">
         <x:v>NOMBRE DE LA AMENIDAD</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="10" t="str">
         <x:v>NOMBRE DEL RECURSO</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="12" t="str">
         <x:v>NOMBRE</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="12" t="str">
         <x:v>APELLIDO PATERNO</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="12" t="str">
         <x:v>APELLIDO MATERNO</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="I1" s="12" t="str">
         <x:v>CORREO ELECTRÓNICO</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="J1" s="12" t="str">
         <x:v>DÍA DE LA SEMANA</x:v>
       </x:c>
-      <x:c r="K1" s="6" t="str">
+      <x:c r="K1" s="12" t="str">
         <x:v>HORA DE INICIO</x:v>
       </x:c>
-      <x:c r="L1" s="6" t="str">
+      <x:c r="L1" s="12" t="str">
         <x:v>HORA DE TÉRMINO</x:v>
       </x:c>
-      <x:c r="M1" s="6" t="str">
+      <x:c r="M1" s="12" t="str">
         <x:v>CAPACIDAD</x:v>
       </x:c>
     </x:row>
@@ -5401,37 +5727,37 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>NOMBRE DE LA CLASE</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="12" t="str">
         <x:v>DÍA DE LA SEMANA</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>HORA DE INICIO</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="10" t="str">
         <x:v>NÚMERO DE SOCIO</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="12" t="str">
         <x:v>NOMBRE</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="12" t="str">
         <x:v>APELLIDO PATERNO</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="12" t="str">
         <x:v>APELLIDO MATERNO</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="I1" s="10" t="str">
         <x:v>NÚMERO DE MEMBRESÍA</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="J1" s="12" t="str">
         <x:v>FECHA Y HORA DE INSCRIPCIÓN</x:v>
       </x:c>
-      <x:c r="K1" s="6" t="str">
+      <x:c r="K1" s="12" t="str">
         <x:v>FECHA Y HORA DE CANCELACIÓN</x:v>
       </x:c>
     </x:row>
@@ -8023,6 +8349,1472 @@
       <x:c r="K200" s="8"/>
     </x:row>
   </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF1A252F"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="76" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="4" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="34" t="str">
+        <x:v>INSTRUCCIONES DE CAPTURA</x:v>
+      </x:c>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="34"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="35"/>
+      <x:c r="B2" s="35"/>
+      <x:c r="C2" s="35"/>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="36" t="str">
+        <x:v>REGLAS GENERALES</x:v>
+      </x:c>
+      <x:c r="B3" s="36"/>
+      <x:c r="C3" s="36"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="37" t="str">
+        <x:v>ENCABEZADOS</x:v>
+      </x:c>
+      <x:c r="B4" s="38" t="str">
+        <x:v>No modificar los encabezados de las hojas de captura.</x:v>
+      </x:c>
+      <x:c r="C4" s="38"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="37" t="str">
+        <x:v>FECHAS</x:v>
+      </x:c>
+      <x:c r="B5" s="38" t="str">
+        <x:v>Usar formato AAAA-MM-DD. Para fecha y hora: AAAA-MM-DD HH:MM.</x:v>
+      </x:c>
+      <x:c r="C5" s="38"/>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="37" t="str">
+        <x:v>DATOS DESCONOCIDOS</x:v>
+      </x:c>
+      <x:c r="B6" s="38" t="str">
+        <x:v>Dejar la celda vacía cuando no se cuente con el dato.</x:v>
+      </x:c>
+      <x:c r="C6" s="38"/>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="37" t="str">
+        <x:v>REFERENCIAS</x:v>
+      </x:c>
+      <x:c r="B7" s="38" t="str">
+        <x:v>Repetir nombre, número de socio, membresía o folio; no usar IDs internos.</x:v>
+      </x:c>
+      <x:c r="C7" s="38"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="37" t="str">
+        <x:v>EJEMPLOS</x:v>
+      </x:c>
+      <x:c r="B8" s="38" t="str">
+        <x:v>La hoja EJEMPLOS es solo guía y no se debe importar como información real.</x:v>
+      </x:c>
+      <x:c r="C8" s="38"/>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="35"/>
+      <x:c r="B9" s="35"/>
+      <x:c r="C9" s="35"/>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="36" t="str">
+        <x:v>LEYENDA DE COLORES</x:v>
+      </x:c>
+      <x:c r="B10" s="36"/>
+      <x:c r="C10" s="36"/>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="39" t="str">
+        <x:v>ENCABEZADO ROJO</x:v>
+      </x:c>
+      <x:c r="B11" s="39" t="str">
+        <x:v>Campo básico para identificar o registrar el dato.</x:v>
+      </x:c>
+      <x:c r="C11" s="39"/>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="40" t="str">
+        <x:v>ENCABEZADO AZUL</x:v>
+      </x:c>
+      <x:c r="B12" s="40" t="str">
+        <x:v>Campo opcional; llenar cuando se cuente con la información.</x:v>
+      </x:c>
+      <x:c r="C12" s="40"/>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="41" t="str">
+        <x:v>ENCABEZADO VERDE</x:v>
+      </x:c>
+      <x:c r="B13" s="41" t="str">
+        <x:v>Catálogo de consulta o solo lectura. No modificar.</x:v>
+      </x:c>
+      <x:c r="C13" s="41"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:C1"/>
+    <x:mergeCell ref="A3:C3"/>
+    <x:mergeCell ref="A10:C10"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF1A252F"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="83" t="str">
+        <x:v>EJEMPLOS: AMENIDADES</x:v>
+      </x:c>
+      <x:c r="B1" s="83"/>
+      <x:c r="C1" s="83"/>
+      <x:c r="D1" s="83"/>
+      <x:c r="E1" s="83"/>
+      <x:c r="F1" s="83"/>
+      <x:c r="G1" s="83"/>
+      <x:c r="H1" s="83"/>
+    </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="89" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="B2" s="89" t="str">
+        <x:v>NOMBRE DE LA AMENIDAD</x:v>
+      </x:c>
+      <x:c r="C2" s="95" t="str">
+        <x:v>DESCRIPCIÓN</x:v>
+      </x:c>
+      <x:c r="D2" s="95" t="str">
+        <x:v>TIPO DE RESERVACIÓN</x:v>
+      </x:c>
+      <x:c r="E2" s="95" t="str">
+        <x:v>ACTIVA</x:v>
+      </x:c>
+      <x:c r="F2" s="95" t="str">
+        <x:v>NOMBRE O RUTA DEL ÍCONO</x:v>
+      </x:c>
+      <x:c r="G2" s="95" t="str">
+        <x:v>NOMBRE O RUTA DE LA IMAGEN</x:v>
+      </x:c>
+      <x:c r="H2" s="95" t="str">
+        <x:v>NOMBRE O RUTA DEL REGLAMENTO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B3" s="100" t="str">
+        <x:v>ALBERCA</x:v>
+      </x:c>
+      <x:c r="C3" s="100" t="str">
+        <x:v>Registro de ejemplo para el socio 1001.</x:v>
+      </x:c>
+      <x:c r="D3" s="100" t="str">
+        <x:v>DATOS DE EJEMPLO 1</x:v>
+      </x:c>
+      <x:c r="E3" s="101" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="F3" s="100" t="str">
+        <x:v>documentos/socio-1001.pdf</x:v>
+      </x:c>
+      <x:c r="G3" s="100" t="str">
+        <x:v>documentos/socio-1001.pdf</x:v>
+      </x:c>
+      <x:c r="H3" s="100" t="str">
+        <x:v>documentos/socio-1001.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B4" s="100" t="str">
+        <x:v>GIMNASIO</x:v>
+      </x:c>
+      <x:c r="C4" s="100" t="str">
+        <x:v>Registro de ejemplo para el socio 1002.</x:v>
+      </x:c>
+      <x:c r="D4" s="100" t="str">
+        <x:v>DATOS DE EJEMPLO 2</x:v>
+      </x:c>
+      <x:c r="E4" s="101" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F4" s="100" t="str">
+        <x:v>documentos/socio-1002.pdf</x:v>
+      </x:c>
+      <x:c r="G4" s="100" t="str">
+        <x:v>documentos/socio-1002.pdf</x:v>
+      </x:c>
+      <x:c r="H4" s="100" t="str">
+        <x:v>documentos/socio-1002.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B5" s="100" t="str">
+        <x:v>CANCHA DE TENIS</x:v>
+      </x:c>
+      <x:c r="C5" s="100" t="str">
+        <x:v>Registro de ejemplo para el socio 1003.</x:v>
+      </x:c>
+      <x:c r="D5" s="100" t="str">
+        <x:v>DATOS DE EJEMPLO 3</x:v>
+      </x:c>
+      <x:c r="E5" s="101" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F5" s="100" t="str">
+        <x:v>documentos/socio-1003.pdf</x:v>
+      </x:c>
+      <x:c r="G5" s="100" t="str">
+        <x:v>documentos/socio-1003.pdf</x:v>
+      </x:c>
+      <x:c r="H5" s="100" t="str">
+        <x:v>documentos/socio-1003.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6"/>
+      <x:c r="B6"/>
+      <x:c r="C6"/>
+      <x:c r="D6"/>
+      <x:c r="E6"/>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="83" t="str">
+        <x:v>EJEMPLOS: HORARIOS AMENIDADES</x:v>
+      </x:c>
+      <x:c r="B8" s="83"/>
+      <x:c r="C8" s="83"/>
+      <x:c r="D8" s="83"/>
+      <x:c r="E8" s="83"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="89" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="B9" s="89" t="str">
+        <x:v>NOMBRE DE LA AMENIDAD</x:v>
+      </x:c>
+      <x:c r="C9" s="95" t="str">
+        <x:v>DÍA DE LA SEMANA</x:v>
+      </x:c>
+      <x:c r="D9" s="95" t="str">
+        <x:v>HORA DE APERTURA</x:v>
+      </x:c>
+      <x:c r="E9" s="95" t="str">
+        <x:v>HORA DE CIERRE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B10" s="100" t="str">
+        <x:v>ALBERCA</x:v>
+      </x:c>
+      <x:c r="C10" s="100" t="str">
+        <x:v>LUNES</x:v>
+      </x:c>
+      <x:c r="D10" s="100" t="str">
+        <x:v>09:00</x:v>
+      </x:c>
+      <x:c r="E10" s="100" t="str">
+        <x:v>09:00</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B11" s="100" t="str">
+        <x:v>GIMNASIO</x:v>
+      </x:c>
+      <x:c r="C11" s="100" t="str">
+        <x:v>MIÉRCOLES</x:v>
+      </x:c>
+      <x:c r="D11" s="100" t="str">
+        <x:v>12:00</x:v>
+      </x:c>
+      <x:c r="E11" s="100" t="str">
+        <x:v>12:00</x:v>
+      </x:c>
+      <x:c r="F11"/>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B12" s="100" t="str">
+        <x:v>CANCHA DE TENIS</x:v>
+      </x:c>
+      <x:c r="C12" s="100" t="str">
+        <x:v>SÁBADO</x:v>
+      </x:c>
+      <x:c r="D12" s="100" t="str">
+        <x:v>18:00</x:v>
+      </x:c>
+      <x:c r="E12" s="100" t="str">
+        <x:v>18:00</x:v>
+      </x:c>
+      <x:c r="F12"/>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="83" t="str">
+        <x:v>EJEMPLOS: RECURSOS</x:v>
+      </x:c>
+      <x:c r="B15" s="83"/>
+      <x:c r="C15" s="83"/>
+      <x:c r="D15" s="83"/>
+      <x:c r="E15" s="83"/>
+      <x:c r="F15" s="83"/>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="89" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="B16" s="89" t="str">
+        <x:v>NOMBRE DE LA AMENIDAD</x:v>
+      </x:c>
+      <x:c r="C16" s="89" t="str">
+        <x:v>NOMBRE DEL RECURSO</x:v>
+      </x:c>
+      <x:c r="D16" s="95" t="str">
+        <x:v>CAPACIDAD</x:v>
+      </x:c>
+      <x:c r="E16" s="95" t="str">
+        <x:v>DURACIÓN DEL TURNO EN MINUTOS</x:v>
+      </x:c>
+      <x:c r="F16" s="95" t="str">
+        <x:v>ACTIVO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B17" s="100" t="str">
+        <x:v>ALBERCA</x:v>
+      </x:c>
+      <x:c r="C17" s="100" t="str">
+        <x:v>CARRIL 1</x:v>
+      </x:c>
+      <x:c r="D17" s="100" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E17" s="100" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F17" s="100" t="str">
+        <x:v>SÍ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B18" s="100" t="str">
+        <x:v>GIMNASIO</x:v>
+      </x:c>
+      <x:c r="C18" s="100" t="str">
+        <x:v>SALA 2</x:v>
+      </x:c>
+      <x:c r="D18" s="100" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E18" s="100" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F18" s="100" t="str">
+        <x:v>SÍ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B19" s="100" t="str">
+        <x:v>CANCHA DE TENIS</x:v>
+      </x:c>
+      <x:c r="C19" s="100" t="str">
+        <x:v>CANCHA 3</x:v>
+      </x:c>
+      <x:c r="D19" s="100" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E19" s="100" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F19" s="100" t="str">
+        <x:v>SÍ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+    </x:row>
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="83" t="str">
+        <x:v>EJEMPLOS: UBICACIONES RECURSOS</x:v>
+      </x:c>
+      <x:c r="B22" s="83"/>
+      <x:c r="C22" s="83"/>
+      <x:c r="D22" s="83"/>
+      <x:c r="E22" s="83"/>
+      <x:c r="F22" s="83"/>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="89" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="B23" s="89" t="str">
+        <x:v>NOMBRE DE LA AMENIDAD</x:v>
+      </x:c>
+      <x:c r="C23" s="89" t="str">
+        <x:v>NOMBRE DEL RECURSO</x:v>
+      </x:c>
+      <x:c r="D23" s="95" t="str">
+        <x:v>LATITUD</x:v>
+      </x:c>
+      <x:c r="E23" s="95" t="str">
+        <x:v>LONGITUD</x:v>
+      </x:c>
+      <x:c r="F23" s="95" t="str">
+        <x:v>ACTIVA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B24" s="100" t="str">
+        <x:v>ALBERCA</x:v>
+      </x:c>
+      <x:c r="C24" s="100" t="str">
+        <x:v>CARRIL 1</x:v>
+      </x:c>
+      <x:c r="D24" s="100" t="n">
+        <x:v>20.6736</x:v>
+      </x:c>
+      <x:c r="E24" s="100" t="n">
+        <x:v>-103.344</x:v>
+      </x:c>
+      <x:c r="F24" s="101" t="n">
+        <x:v>400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B25" s="100" t="str">
+        <x:v>GIMNASIO</x:v>
+      </x:c>
+      <x:c r="C25" s="100" t="str">
+        <x:v>SALA 2</x:v>
+      </x:c>
+      <x:c r="D25" s="100" t="n">
+        <x:v>20.6746</x:v>
+      </x:c>
+      <x:c r="E25" s="100" t="n">
+        <x:v>-103.34299999999999</x:v>
+      </x:c>
+      <x:c r="F25" s="101" t="n">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="24" customHeight="1">
+      <x:c r="A26" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B26" s="100" t="str">
+        <x:v>CANCHA DE TENIS</x:v>
+      </x:c>
+      <x:c r="C26" s="100" t="str">
+        <x:v>CANCHA 3</x:v>
+      </x:c>
+      <x:c r="D26" s="100" t="n">
+        <x:v>20.6756</x:v>
+      </x:c>
+      <x:c r="E26" s="100" t="n">
+        <x:v>-103.342</x:v>
+      </x:c>
+      <x:c r="F26" s="101" t="n">
+        <x:v>192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="42" customHeight="1">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+    </x:row>
+    <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+    </x:row>
+    <x:row r="29" ht="24" customHeight="1">
+      <x:c r="A29" s="83" t="str">
+        <x:v>EJEMPLOS: PERIODOS BLOQUEADOS</x:v>
+      </x:c>
+      <x:c r="B29" s="83"/>
+      <x:c r="C29" s="83"/>
+      <x:c r="D29" s="83"/>
+      <x:c r="E29" s="83"/>
+      <x:c r="F29" s="83"/>
+    </x:row>
+    <x:row r="30" ht="42" customHeight="1">
+      <x:c r="A30" s="89" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="B30" s="89" t="str">
+        <x:v>NOMBRE DE LA AMENIDAD</x:v>
+      </x:c>
+      <x:c r="C30" s="89" t="str">
+        <x:v>NOMBRE DEL RECURSO</x:v>
+      </x:c>
+      <x:c r="D30" s="95" t="str">
+        <x:v>FECHA Y HORA DE INICIO</x:v>
+      </x:c>
+      <x:c r="E30" s="95" t="str">
+        <x:v>FECHA Y HORA DE TÉRMINO</x:v>
+      </x:c>
+      <x:c r="F30" s="95" t="str">
+        <x:v>MOTIVO DEL BLOQUEO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="24" customHeight="1">
+      <x:c r="A31" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B31" s="100" t="str">
+        <x:v>ALBERCA</x:v>
+      </x:c>
+      <x:c r="C31" s="100" t="str">
+        <x:v>CARRIL 1</x:v>
+      </x:c>
+      <x:c r="D31" s="102" t="n">
+        <x:v>46037.625</x:v>
+      </x:c>
+      <x:c r="E31" s="102" t="n">
+        <x:v>46037.625</x:v>
+      </x:c>
+      <x:c r="F31" s="100" t="str">
+        <x:v>Registro de ejemplo para el socio 1001.</x:v>
+      </x:c>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
+    </x:row>
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B32" s="100" t="str">
+        <x:v>GIMNASIO</x:v>
+      </x:c>
+      <x:c r="C32" s="100" t="str">
+        <x:v>SALA 2</x:v>
+      </x:c>
+      <x:c r="D32" s="102" t="n">
+        <x:v>46044.666666666664</x:v>
+      </x:c>
+      <x:c r="E32" s="102" t="n">
+        <x:v>46044.666666666664</x:v>
+      </x:c>
+      <x:c r="F32" s="100" t="str">
+        <x:v>Registro de ejemplo para el socio 1002.</x:v>
+      </x:c>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+    </x:row>
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B33" s="100" t="str">
+        <x:v>CANCHA DE TENIS</x:v>
+      </x:c>
+      <x:c r="C33" s="100" t="str">
+        <x:v>CANCHA 3</x:v>
+      </x:c>
+      <x:c r="D33" s="102" t="n">
+        <x:v>46051.708333333336</x:v>
+      </x:c>
+      <x:c r="E33" s="102" t="n">
+        <x:v>46051.708333333336</x:v>
+      </x:c>
+      <x:c r="F33" s="100" t="str">
+        <x:v>Registro de ejemplo para el socio 1003.</x:v>
+      </x:c>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
+    </x:row>
+    <x:row r="36" ht="24" customHeight="1">
+      <x:c r="A36" s="83" t="str">
+        <x:v>EJEMPLOS: ESPECIALIDADES</x:v>
+      </x:c>
+      <x:c r="B36" s="83"/>
+      <x:c r="C36" s="83"/>
+      <x:c r="D36" s="83"/>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
+    </x:row>
+    <x:row r="37" ht="42" customHeight="1">
+      <x:c r="A37" s="89" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="B37" s="89" t="str">
+        <x:v>CLAVE</x:v>
+      </x:c>
+      <x:c r="C37" s="95" t="str">
+        <x:v>NOMBRE DE LA ESPECIALIDAD</x:v>
+      </x:c>
+      <x:c r="D37" s="95" t="str">
+        <x:v>ACTIVA</x:v>
+      </x:c>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
+    </x:row>
+    <x:row r="38" ht="24" customHeight="1">
+      <x:c r="A38" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B38" s="100" t="str">
+        <x:v>EJ-001</x:v>
+      </x:c>
+      <x:c r="C38" s="100" t="str">
+        <x:v>NATACIÓN</x:v>
+      </x:c>
+      <x:c r="D38" s="101" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E38"/>
+      <x:c r="F38"/>
+    </x:row>
+    <x:row r="39" ht="24" customHeight="1">
+      <x:c r="A39" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B39" s="100" t="str">
+        <x:v>EJ-002</x:v>
+      </x:c>
+      <x:c r="C39" s="100" t="str">
+        <x:v>ACONDICIONAMIENTO FÍSICO</x:v>
+      </x:c>
+      <x:c r="D39" s="101" t="n">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="24" customHeight="1">
+      <x:c r="A40" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B40" s="100" t="str">
+        <x:v>EJ-003</x:v>
+      </x:c>
+      <x:c r="C40" s="100" t="str">
+        <x:v>TENIS</x:v>
+      </x:c>
+      <x:c r="D40" s="101" t="n">
+        <x:v>192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="24" customHeight="1">
+      <x:c r="A41"/>
+      <x:c r="B41"/>
+      <x:c r="C41"/>
+      <x:c r="D41"/>
+      <x:c r="E41"/>
+      <x:c r="F41"/>
+      <x:c r="G41"/>
+      <x:c r="H41"/>
+    </x:row>
+    <x:row r="42" ht="42" customHeight="1">
+      <x:c r="A42"/>
+      <x:c r="B42"/>
+      <x:c r="C42"/>
+      <x:c r="D42"/>
+      <x:c r="E42"/>
+      <x:c r="F42"/>
+      <x:c r="G42"/>
+      <x:c r="H42"/>
+    </x:row>
+    <x:row r="43" ht="24" customHeight="1">
+      <x:c r="A43" s="83" t="str">
+        <x:v>EJEMPLOS: ENTRENADORES</x:v>
+      </x:c>
+      <x:c r="B43" s="83"/>
+      <x:c r="C43" s="83"/>
+      <x:c r="D43" s="83"/>
+      <x:c r="E43" s="83"/>
+      <x:c r="F43" s="83"/>
+      <x:c r="G43" s="83"/>
+      <x:c r="H43" s="83"/>
+    </x:row>
+    <x:row r="44" ht="42" customHeight="1">
+      <x:c r="A44" s="89" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="B44" s="95" t="str">
+        <x:v>NOMBRE</x:v>
+      </x:c>
+      <x:c r="C44" s="95" t="str">
+        <x:v>APELLIDO PATERNO</x:v>
+      </x:c>
+      <x:c r="D44" s="95" t="str">
+        <x:v>APELLIDO MATERNO</x:v>
+      </x:c>
+      <x:c r="E44" s="95" t="str">
+        <x:v>CORREO ELECTRÓNICO</x:v>
+      </x:c>
+      <x:c r="F44" s="95" t="str">
+        <x:v>TELÉFONO</x:v>
+      </x:c>
+      <x:c r="G44" s="89" t="str">
+        <x:v>NOMBRE DE LA AMENIDAD PRINCIPAL</x:v>
+      </x:c>
+      <x:c r="H44" s="95" t="str">
+        <x:v>NOMBRE O RUTA DE LA FOTOGRAFÍA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="24" customHeight="1">
+      <x:c r="A45" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B45" s="100" t="str">
+        <x:v>Andrea</x:v>
+      </x:c>
+      <x:c r="C45" s="100" t="str">
+        <x:v>Ruiz</x:v>
+      </x:c>
+      <x:c r="D45" s="100" t="str">
+        <x:v>Torres</x:v>
+      </x:c>
+      <x:c r="E45" s="100" t="str">
+        <x:v>andrea.ruiz@example.com</x:v>
+      </x:c>
+      <x:c r="F45" s="100" t="str">
+        <x:v>3345678901</x:v>
+      </x:c>
+      <x:c r="G45" s="100" t="str">
+        <x:v>ALBERCA</x:v>
+      </x:c>
+      <x:c r="H45" s="100" t="str">
+        <x:v>documentos/socio-1001.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="24" customHeight="1">
+      <x:c r="A46" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B46" s="100" t="str">
+        <x:v>Carlos</x:v>
+      </x:c>
+      <x:c r="C46" s="100" t="str">
+        <x:v>Mendoza</x:v>
+      </x:c>
+      <x:c r="D46" s="100" t="str">
+        <x:v>Vega</x:v>
+      </x:c>
+      <x:c r="E46" s="100" t="str">
+        <x:v>carlos.mendoza@example.com</x:v>
+      </x:c>
+      <x:c r="F46" s="100" t="str">
+        <x:v>3356789012</x:v>
+      </x:c>
+      <x:c r="G46" s="100" t="str">
+        <x:v>GIMNASIO</x:v>
+      </x:c>
+      <x:c r="H46" s="100" t="str">
+        <x:v>documentos/socio-1002.pdf</x:v>
+      </x:c>
+      <x:c r="I46"/>
+      <x:c r="J46"/>
+      <x:c r="K46"/>
+      <x:c r="L46"/>
+      <x:c r="M46"/>
+    </x:row>
+    <x:row r="47" ht="24" customHeight="1">
+      <x:c r="A47" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B47" s="100" t="str">
+        <x:v>Sofía</x:v>
+      </x:c>
+      <x:c r="C47" s="100" t="str">
+        <x:v>Navarro</x:v>
+      </x:c>
+      <x:c r="D47" s="100" t="str">
+        <x:v>Cruz</x:v>
+      </x:c>
+      <x:c r="E47" s="100" t="str">
+        <x:v>sofia.navarro@example.com</x:v>
+      </x:c>
+      <x:c r="F47" s="100" t="str">
+        <x:v>3367890123</x:v>
+      </x:c>
+      <x:c r="G47" s="100" t="str">
+        <x:v>CANCHA DE TENIS</x:v>
+      </x:c>
+      <x:c r="H47" s="100" t="str">
+        <x:v>documentos/socio-1003.pdf</x:v>
+      </x:c>
+      <x:c r="I47"/>
+      <x:c r="J47"/>
+      <x:c r="K47"/>
+      <x:c r="L47"/>
+      <x:c r="M47"/>
+    </x:row>
+    <x:row r="48" ht="24" customHeight="1">
+      <x:c r="A48"/>
+      <x:c r="B48"/>
+      <x:c r="C48"/>
+      <x:c r="D48"/>
+      <x:c r="E48"/>
+      <x:c r="F48"/>
+      <x:c r="G48"/>
+      <x:c r="H48"/>
+      <x:c r="I48"/>
+      <x:c r="J48"/>
+      <x:c r="K48"/>
+      <x:c r="L48"/>
+      <x:c r="M48"/>
+    </x:row>
+    <x:row r="50" ht="24" customHeight="1">
+      <x:c r="A50" s="83" t="str">
+        <x:v>EJEMPLOS: ESPECIALIDADES ENTRENADOR</x:v>
+      </x:c>
+      <x:c r="B50" s="83"/>
+      <x:c r="C50" s="83"/>
+      <x:c r="D50" s="83"/>
+      <x:c r="E50" s="83"/>
+      <x:c r="F50" s="83"/>
+    </x:row>
+    <x:row r="51" ht="42" customHeight="1">
+      <x:c r="A51" s="89" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="B51" s="95" t="str">
+        <x:v>NOMBRE</x:v>
+      </x:c>
+      <x:c r="C51" s="95" t="str">
+        <x:v>APELLIDO PATERNO</x:v>
+      </x:c>
+      <x:c r="D51" s="95" t="str">
+        <x:v>APELLIDO MATERNO</x:v>
+      </x:c>
+      <x:c r="E51" s="95" t="str">
+        <x:v>CORREO ELECTRÓNICO</x:v>
+      </x:c>
+      <x:c r="F51" s="95" t="str">
+        <x:v>NOMBRE DE LA ESPECIALIDAD</x:v>
+      </x:c>
+      <x:c r="G51"/>
+      <x:c r="H51"/>
+      <x:c r="I51"/>
+      <x:c r="J51"/>
+      <x:c r="K51"/>
+    </x:row>
+    <x:row r="52" ht="24" customHeight="1">
+      <x:c r="A52" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B52" s="100" t="str">
+        <x:v>Andrea</x:v>
+      </x:c>
+      <x:c r="C52" s="100" t="str">
+        <x:v>Ruiz</x:v>
+      </x:c>
+      <x:c r="D52" s="100" t="str">
+        <x:v>Torres</x:v>
+      </x:c>
+      <x:c r="E52" s="100" t="str">
+        <x:v>andrea.ruiz@example.com</x:v>
+      </x:c>
+      <x:c r="F52" s="100" t="str">
+        <x:v>NATACIÓN</x:v>
+      </x:c>
+      <x:c r="G52"/>
+      <x:c r="H52"/>
+      <x:c r="I52"/>
+      <x:c r="J52"/>
+      <x:c r="K52"/>
+    </x:row>
+    <x:row r="53" ht="24" customHeight="1">
+      <x:c r="A53" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B53" s="100" t="str">
+        <x:v>Carlos</x:v>
+      </x:c>
+      <x:c r="C53" s="100" t="str">
+        <x:v>Mendoza</x:v>
+      </x:c>
+      <x:c r="D53" s="100" t="str">
+        <x:v>Vega</x:v>
+      </x:c>
+      <x:c r="E53" s="100" t="str">
+        <x:v>carlos.mendoza@example.com</x:v>
+      </x:c>
+      <x:c r="F53" s="100" t="str">
+        <x:v>ACONDICIONAMIENTO FÍSICO</x:v>
+      </x:c>
+      <x:c r="G53"/>
+      <x:c r="H53"/>
+      <x:c r="I53"/>
+      <x:c r="J53"/>
+      <x:c r="K53"/>
+    </x:row>
+    <x:row r="54" ht="24" customHeight="1">
+      <x:c r="A54" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B54" s="100" t="str">
+        <x:v>Sofía</x:v>
+      </x:c>
+      <x:c r="C54" s="100" t="str">
+        <x:v>Navarro</x:v>
+      </x:c>
+      <x:c r="D54" s="100" t="str">
+        <x:v>Cruz</x:v>
+      </x:c>
+      <x:c r="E54" s="100" t="str">
+        <x:v>sofia.navarro@example.com</x:v>
+      </x:c>
+      <x:c r="F54" s="100" t="str">
+        <x:v>TENIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="24" customHeight="1">
+      <x:c r="A57" s="83" t="str">
+        <x:v>EJEMPLOS: DISPONIBILIDAD ENTRENADORES</x:v>
+      </x:c>
+      <x:c r="B57" s="83"/>
+      <x:c r="C57" s="83"/>
+      <x:c r="D57" s="83"/>
+      <x:c r="E57" s="83"/>
+      <x:c r="F57" s="83"/>
+      <x:c r="G57" s="83"/>
+      <x:c r="H57" s="83"/>
+    </x:row>
+    <x:row r="58" ht="42" customHeight="1">
+      <x:c r="A58" s="89" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="B58" s="95" t="str">
+        <x:v>NOMBRE</x:v>
+      </x:c>
+      <x:c r="C58" s="95" t="str">
+        <x:v>APELLIDO PATERNO</x:v>
+      </x:c>
+      <x:c r="D58" s="95" t="str">
+        <x:v>APELLIDO MATERNO</x:v>
+      </x:c>
+      <x:c r="E58" s="95" t="str">
+        <x:v>CORREO ELECTRÓNICO</x:v>
+      </x:c>
+      <x:c r="F58" s="95" t="str">
+        <x:v>DÍA DE LA SEMANA</x:v>
+      </x:c>
+      <x:c r="G58" s="95" t="str">
+        <x:v>HORA DE INICIO</x:v>
+      </x:c>
+      <x:c r="H58" s="95" t="str">
+        <x:v>HORA DE TÉRMINO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="24" customHeight="1">
+      <x:c r="A59" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B59" s="100" t="str">
+        <x:v>Andrea</x:v>
+      </x:c>
+      <x:c r="C59" s="100" t="str">
+        <x:v>Ruiz</x:v>
+      </x:c>
+      <x:c r="D59" s="100" t="str">
+        <x:v>Torres</x:v>
+      </x:c>
+      <x:c r="E59" s="100" t="str">
+        <x:v>andrea.ruiz@example.com</x:v>
+      </x:c>
+      <x:c r="F59" s="100" t="str">
+        <x:v>LUNES</x:v>
+      </x:c>
+      <x:c r="G59" s="100" t="str">
+        <x:v>09:00</x:v>
+      </x:c>
+      <x:c r="H59" s="100" t="str">
+        <x:v>09:00</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="24" customHeight="1">
+      <x:c r="A60" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B60" s="100" t="str">
+        <x:v>Carlos</x:v>
+      </x:c>
+      <x:c r="C60" s="100" t="str">
+        <x:v>Mendoza</x:v>
+      </x:c>
+      <x:c r="D60" s="100" t="str">
+        <x:v>Vega</x:v>
+      </x:c>
+      <x:c r="E60" s="100" t="str">
+        <x:v>carlos.mendoza@example.com</x:v>
+      </x:c>
+      <x:c r="F60" s="100" t="str">
+        <x:v>MIÉRCOLES</x:v>
+      </x:c>
+      <x:c r="G60" s="100" t="str">
+        <x:v>12:00</x:v>
+      </x:c>
+      <x:c r="H60" s="100" t="str">
+        <x:v>12:00</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="24" customHeight="1">
+      <x:c r="A61" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B61" s="100" t="str">
+        <x:v>Sofía</x:v>
+      </x:c>
+      <x:c r="C61" s="100" t="str">
+        <x:v>Navarro</x:v>
+      </x:c>
+      <x:c r="D61" s="100" t="str">
+        <x:v>Cruz</x:v>
+      </x:c>
+      <x:c r="E61" s="100" t="str">
+        <x:v>sofia.navarro@example.com</x:v>
+      </x:c>
+      <x:c r="F61" s="100" t="str">
+        <x:v>SÁBADO</x:v>
+      </x:c>
+      <x:c r="G61" s="100" t="str">
+        <x:v>18:00</x:v>
+      </x:c>
+      <x:c r="H61" s="100" t="str">
+        <x:v>18:00</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="24" customHeight="1">
+      <x:c r="A64" s="83" t="str">
+        <x:v>EJEMPLOS: HORARIOS DE CLASES</x:v>
+      </x:c>
+      <x:c r="B64" s="83"/>
+      <x:c r="C64" s="83"/>
+      <x:c r="D64" s="83"/>
+      <x:c r="E64" s="83"/>
+      <x:c r="F64" s="83"/>
+      <x:c r="G64" s="83"/>
+      <x:c r="H64" s="83"/>
+      <x:c r="I64" s="83"/>
+      <x:c r="J64" s="83"/>
+      <x:c r="K64" s="83"/>
+      <x:c r="L64" s="83"/>
+      <x:c r="M64" s="83"/>
+    </x:row>
+    <x:row r="65" ht="42" customHeight="1">
+      <x:c r="A65" s="89" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="B65" s="89" t="str">
+        <x:v>NOMBRE DE LA CLASE</x:v>
+      </x:c>
+      <x:c r="C65" s="95" t="str">
+        <x:v>TIPO DE CLASE</x:v>
+      </x:c>
+      <x:c r="D65" s="89" t="str">
+        <x:v>NOMBRE DE LA AMENIDAD</x:v>
+      </x:c>
+      <x:c r="E65" s="89" t="str">
+        <x:v>NOMBRE DEL RECURSO</x:v>
+      </x:c>
+      <x:c r="F65" s="95" t="str">
+        <x:v>NOMBRE</x:v>
+      </x:c>
+      <x:c r="G65" s="95" t="str">
+        <x:v>APELLIDO PATERNO</x:v>
+      </x:c>
+      <x:c r="H65" s="95" t="str">
+        <x:v>APELLIDO MATERNO</x:v>
+      </x:c>
+      <x:c r="I65" s="95" t="str">
+        <x:v>CORREO ELECTRÓNICO</x:v>
+      </x:c>
+      <x:c r="J65" s="95" t="str">
+        <x:v>DÍA DE LA SEMANA</x:v>
+      </x:c>
+      <x:c r="K65" s="95" t="str">
+        <x:v>HORA DE INICIO</x:v>
+      </x:c>
+      <x:c r="L65" s="95" t="str">
+        <x:v>HORA DE TÉRMINO</x:v>
+      </x:c>
+      <x:c r="M65" s="95" t="str">
+        <x:v>CAPACIDAD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="24" customHeight="1">
+      <x:c r="A66" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B66" s="100" t="str">
+        <x:v>NATACIÓN MATUTINA</x:v>
+      </x:c>
+      <x:c r="C66" s="100" t="str">
+        <x:v>DATOS DE EJEMPLO 1</x:v>
+      </x:c>
+      <x:c r="D66" s="100" t="str">
+        <x:v>ALBERCA</x:v>
+      </x:c>
+      <x:c r="E66" s="100" t="str">
+        <x:v>CARRIL 1</x:v>
+      </x:c>
+      <x:c r="F66" s="100" t="str">
+        <x:v>Juan Carlos</x:v>
+      </x:c>
+      <x:c r="G66" s="100" t="str">
+        <x:v>Pérez</x:v>
+      </x:c>
+      <x:c r="H66" s="100" t="str">
+        <x:v>Hernández</x:v>
+      </x:c>
+      <x:c r="I66" s="100" t="str">
+        <x:v>juan.perez@example.com</x:v>
+      </x:c>
+      <x:c r="J66" s="100" t="str">
+        <x:v>LUNES</x:v>
+      </x:c>
+      <x:c r="K66" s="100" t="str">
+        <x:v>09:00</x:v>
+      </x:c>
+      <x:c r="L66" s="100" t="str">
+        <x:v>09:00</x:v>
+      </x:c>
+      <x:c r="M66" s="100" t="n">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="24" customHeight="1">
+      <x:c r="A67" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B67" s="100" t="str">
+        <x:v>YOGA</x:v>
+      </x:c>
+      <x:c r="C67" s="100" t="str">
+        <x:v>DATOS DE EJEMPLO 2</x:v>
+      </x:c>
+      <x:c r="D67" s="100" t="str">
+        <x:v>GIMNASIO</x:v>
+      </x:c>
+      <x:c r="E67" s="100" t="str">
+        <x:v>SALA 2</x:v>
+      </x:c>
+      <x:c r="F67" s="100" t="str">
+        <x:v>María Fernanda</x:v>
+      </x:c>
+      <x:c r="G67" s="100" t="str">
+        <x:v>López</x:v>
+      </x:c>
+      <x:c r="H67" s="100" t="str">
+        <x:v>García</x:v>
+      </x:c>
+      <x:c r="I67" s="100" t="str">
+        <x:v>maria.lopez@example.com</x:v>
+      </x:c>
+      <x:c r="J67" s="100" t="str">
+        <x:v>MIÉRCOLES</x:v>
+      </x:c>
+      <x:c r="K67" s="100" t="str">
+        <x:v>12:00</x:v>
+      </x:c>
+      <x:c r="L67" s="100" t="str">
+        <x:v>12:00</x:v>
+      </x:c>
+      <x:c r="M67" s="100" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="24" customHeight="1">
+      <x:c r="A68" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B68" s="100" t="str">
+        <x:v>TENIS PARA ADULTOS</x:v>
+      </x:c>
+      <x:c r="C68" s="100" t="str">
+        <x:v>DATOS DE EJEMPLO 3</x:v>
+      </x:c>
+      <x:c r="D68" s="100" t="str">
+        <x:v>CANCHA DE TENIS</x:v>
+      </x:c>
+      <x:c r="E68" s="100" t="str">
+        <x:v>CANCHA 3</x:v>
+      </x:c>
+      <x:c r="F68" s="100" t="str">
+        <x:v>Roberto</x:v>
+      </x:c>
+      <x:c r="G68" s="100" t="str">
+        <x:v>Sánchez</x:v>
+      </x:c>
+      <x:c r="H68" s="100" t="str">
+        <x:v>Morales</x:v>
+      </x:c>
+      <x:c r="I68" s="100" t="str">
+        <x:v>roberto.sanchez@example.com</x:v>
+      </x:c>
+      <x:c r="J68" s="100" t="str">
+        <x:v>SÁBADO</x:v>
+      </x:c>
+      <x:c r="K68" s="100" t="str">
+        <x:v>18:00</x:v>
+      </x:c>
+      <x:c r="L68" s="100" t="str">
+        <x:v>18:00</x:v>
+      </x:c>
+      <x:c r="M68" s="100" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="24" customHeight="1">
+      <x:c r="A71" s="83" t="str">
+        <x:v>EJEMPLOS: INSCRIPCIONES A CLASES</x:v>
+      </x:c>
+      <x:c r="B71" s="83"/>
+      <x:c r="C71" s="83"/>
+      <x:c r="D71" s="83"/>
+      <x:c r="E71" s="83"/>
+      <x:c r="F71" s="83"/>
+      <x:c r="G71" s="83"/>
+      <x:c r="H71" s="83"/>
+      <x:c r="I71" s="83"/>
+      <x:c r="J71" s="83"/>
+      <x:c r="K71" s="83"/>
+    </x:row>
+    <x:row r="72" ht="42" customHeight="1">
+      <x:c r="A72" s="89" t="str">
+        <x:v>NOMBRE DEL CLUB</x:v>
+      </x:c>
+      <x:c r="B72" s="89" t="str">
+        <x:v>NOMBRE DE LA CLASE</x:v>
+      </x:c>
+      <x:c r="C72" s="95" t="str">
+        <x:v>DÍA DE LA SEMANA</x:v>
+      </x:c>
+      <x:c r="D72" s="95" t="str">
+        <x:v>HORA DE INICIO</x:v>
+      </x:c>
+      <x:c r="E72" s="89" t="str">
+        <x:v>NÚMERO DE SOCIO</x:v>
+      </x:c>
+      <x:c r="F72" s="95" t="str">
+        <x:v>NOMBRE</x:v>
+      </x:c>
+      <x:c r="G72" s="95" t="str">
+        <x:v>APELLIDO PATERNO</x:v>
+      </x:c>
+      <x:c r="H72" s="95" t="str">
+        <x:v>APELLIDO MATERNO</x:v>
+      </x:c>
+      <x:c r="I72" s="89" t="str">
+        <x:v>NÚMERO DE MEMBRESÍA</x:v>
+      </x:c>
+      <x:c r="J72" s="95" t="str">
+        <x:v>FECHA Y HORA DE INSCRIPCIÓN</x:v>
+      </x:c>
+      <x:c r="K72" s="95" t="str">
+        <x:v>FECHA Y HORA DE CANCELACIÓN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="24" customHeight="1">
+      <x:c r="A73" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B73" s="100" t="str">
+        <x:v>NATACIÓN MATUTINA</x:v>
+      </x:c>
+      <x:c r="C73" s="100" t="str">
+        <x:v>LUNES</x:v>
+      </x:c>
+      <x:c r="D73" s="100" t="str">
+        <x:v>09:00</x:v>
+      </x:c>
+      <x:c r="E73" s="100" t="str">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="F73" s="100" t="str">
+        <x:v>Juan Carlos</x:v>
+      </x:c>
+      <x:c r="G73" s="100" t="str">
+        <x:v>Pérez</x:v>
+      </x:c>
+      <x:c r="H73" s="100" t="str">
+        <x:v>Hernández</x:v>
+      </x:c>
+      <x:c r="I73" s="100" t="str">
+        <x:v>M-1001</x:v>
+      </x:c>
+      <x:c r="J73" s="102" t="n">
+        <x:v>46037.625</x:v>
+      </x:c>
+      <x:c r="K73" s="102" t="n">
+        <x:v>46037.625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="24" customHeight="1">
+      <x:c r="A74" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B74" s="100" t="str">
+        <x:v>YOGA</x:v>
+      </x:c>
+      <x:c r="C74" s="100" t="str">
+        <x:v>MIÉRCOLES</x:v>
+      </x:c>
+      <x:c r="D74" s="100" t="str">
+        <x:v>12:00</x:v>
+      </x:c>
+      <x:c r="E74" s="100" t="str">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="F74" s="100" t="str">
+        <x:v>María Fernanda</x:v>
+      </x:c>
+      <x:c r="G74" s="100" t="str">
+        <x:v>López</x:v>
+      </x:c>
+      <x:c r="H74" s="100" t="str">
+        <x:v>García</x:v>
+      </x:c>
+      <x:c r="I74" s="100" t="str">
+        <x:v>M-1002</x:v>
+      </x:c>
+      <x:c r="J74" s="102" t="n">
+        <x:v>46044.666666666664</x:v>
+      </x:c>
+      <x:c r="K74" s="102" t="n">
+        <x:v>46044.666666666664</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="24" customHeight="1">
+      <x:c r="A75" s="100" t="str">
+        <x:v>PARQUE ESPAÑA</x:v>
+      </x:c>
+      <x:c r="B75" s="100" t="str">
+        <x:v>TENIS PARA ADULTOS</x:v>
+      </x:c>
+      <x:c r="C75" s="100" t="str">
+        <x:v>SÁBADO</x:v>
+      </x:c>
+      <x:c r="D75" s="100" t="str">
+        <x:v>18:00</x:v>
+      </x:c>
+      <x:c r="E75" s="100" t="str">
+        <x:v>1003</x:v>
+      </x:c>
+      <x:c r="F75" s="100" t="str">
+        <x:v>Roberto</x:v>
+      </x:c>
+      <x:c r="G75" s="100" t="str">
+        <x:v>Sánchez</x:v>
+      </x:c>
+      <x:c r="H75" s="100" t="str">
+        <x:v>Morales</x:v>
+      </x:c>
+      <x:c r="I75" s="100" t="str">
+        <x:v>M-1003</x:v>
+      </x:c>
+      <x:c r="J75" s="102" t="n">
+        <x:v>46051.708333333336</x:v>
+      </x:c>
+      <x:c r="K75" s="102" t="n">
+        <x:v>46051.708333333336</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A8:E8"/>
+    <x:mergeCell ref="A15:F15"/>
+    <x:mergeCell ref="A22:F22"/>
+    <x:mergeCell ref="A29:F29"/>
+    <x:mergeCell ref="A36:D36"/>
+    <x:mergeCell ref="A43:H43"/>
+    <x:mergeCell ref="A50:F50"/>
+    <x:mergeCell ref="A57:H57"/>
+    <x:mergeCell ref="A64:M64"/>
+    <x:mergeCell ref="A71:K71"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -8042,19 +9834,19 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>NOMBRE DE LA AMENIDAD</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="12" t="str">
         <x:v>DÍA DE LA SEMANA</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>HORA DE APERTURA</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="12" t="str">
         <x:v>HORA DE CIERRE</x:v>
       </x:c>
     </x:row>
@@ -9472,22 +11264,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>NOMBRE DE LA AMENIDAD</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="10" t="str">
         <x:v>NOMBRE DEL RECURSO</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>CAPACIDAD</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="12" t="str">
         <x:v>DURACIÓN DEL TURNO EN MINUTOS</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="12" t="str">
         <x:v>ACTIVO</x:v>
       </x:c>
     </x:row>
@@ -11104,22 +12896,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>NOMBRE DE LA AMENIDAD</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="10" t="str">
         <x:v>NOMBRE DEL RECURSO</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>LATITUD</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="12" t="str">
         <x:v>LONGITUD</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="12" t="str">
         <x:v>ACTIVA</x:v>
       </x:c>
     </x:row>
@@ -12736,22 +14528,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>NOMBRE DE LA AMENIDAD</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="10" t="str">
         <x:v>NOMBRE DEL RECURSO</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>FECHA Y HORA DE INICIO</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="12" t="str">
         <x:v>FECHA Y HORA DE TÉRMINO</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="12" t="str">
         <x:v>MOTIVO DEL BLOQUEO</x:v>
       </x:c>
     </x:row>
@@ -14366,16 +16158,16 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>CLAVE</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="12" t="str">
         <x:v>NOMBRE DE LA ESPECIALIDAD</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>ACTIVA</x:v>
       </x:c>
     </x:row>
@@ -15596,28 +17388,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="12" t="str">
         <x:v>NOMBRE</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="12" t="str">
         <x:v>APELLIDO PATERNO</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>APELLIDO MATERNO</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="12" t="str">
         <x:v>CORREO ELECTRÓNICO</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="12" t="str">
         <x:v>TELÉFONO</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="10" t="str">
         <x:v>NOMBRE DE LA AMENIDAD PRINCIPAL</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="12" t="str">
         <x:v>NOMBRE O RUTA DE LA FOTOGRAFÍA</x:v>
       </x:c>
     </x:row>
@@ -17632,22 +19424,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="12" t="str">
         <x:v>NOMBRE</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="12" t="str">
         <x:v>APELLIDO PATERNO</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>APELLIDO MATERNO</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="12" t="str">
         <x:v>CORREO ELECTRÓNICO</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="12" t="str">
         <x:v>NOMBRE DE LA ESPECIALIDAD</x:v>
       </x:c>
     </x:row>
@@ -19266,28 +21058,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>NOMBRE DEL CLUB</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="12" t="str">
         <x:v>NOMBRE</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="12" t="str">
         <x:v>APELLIDO PATERNO</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>APELLIDO MATERNO</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="12" t="str">
         <x:v>CORREO ELECTRÓNICO</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="12" t="str">
         <x:v>DÍA DE LA SEMANA</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="12" t="str">
         <x:v>HORA DE INICIO</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="12" t="str">
         <x:v>HORA DE TÉRMINO</x:v>
       </x:c>
     </x:row>

--- a/database/seeders/data/07_AMENIDADES_Y_CLASES.xlsx
+++ b/database/seeders/data/07_AMENIDADES_Y_CLASES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Apache24\htdocs\ParquesEsp\database\seeders\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA9FDF5-8A36-44E8-AA01-F2027FD199C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2016AB26-F1B5-4686-AF2A-A7F26AF4F30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCCIONES" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="250">
   <si>
     <t>INSTRUCCIONES DE CAPTURA</t>
   </si>
@@ -457,27 +457,6 @@
     <t>Ver catálogo CLUBES en 02_CLUBES_Y_CONFIGURACION.</t>
   </si>
   <si>
-    <t>Nombre de la amenidad, ej. 'Alberca', 'Canchas de tenis'.</t>
-  </si>
-  <si>
-    <t>Descripción breve de la amenidad.</t>
-  </si>
-  <si>
-    <t>Una de: Por hora (se reserva un horario específico), Por día (se reserva el día completo, ej. jardines), Por capacidad (se reserva un lugar dentro de un cupo, ej. alberca).</t>
-  </si>
-  <si>
-    <t>SÍ/NO. Si se deja vacío, se considera activa.</t>
-  </si>
-  <si>
-    <t>Nombre del archivo de ícono de la amenidad, si se tiene.</t>
-  </si>
-  <si>
-    <t>Nombre del archivo de imagen de fondo de la amenidad, si se tiene.</t>
-  </si>
-  <si>
-    <t>Nombre del archivo con el reglamento de uso de la amenidad, si se tiene.</t>
-  </si>
-  <si>
     <t>Parque España I</t>
   </si>
   <si>
@@ -534,9 +513,6 @@
     <t>Ver hoja AMENIDADES de este mismo archivo.</t>
   </si>
   <si>
-    <t>Nombre del día (Lunes a Domingo). Una fila por cada día que la amenidad esté disponible.</t>
-  </si>
-  <si>
     <t>Formato HH:MM (24 horas).</t>
   </si>
   <si>
@@ -584,18 +560,6 @@
     </r>
   </si>
   <si>
-    <t>Unidad reservable dentro de la amenidad, ej. 'Cancha 1', 'Jardín 2', 'Asador 3'. Si la amenidad no se divide en unidades (ej. la alberca completa), captura un solo recurso con el mismo nombre que la amenidad.</t>
-  </si>
-  <si>
-    <t>Cupo máximo de este recurso. Déjalo vacío si no aplica.</t>
-  </si>
-  <si>
-    <t>Duración de cada turno reservable, en minutos. Déjalo vacío si no aplica (ej. reservaciones por día completo).</t>
-  </si>
-  <si>
-    <t>SÍ/NO. Si se deja vacío, se considera activo.</t>
-  </si>
-  <si>
     <t>Cancha 1</t>
   </si>
   <si>
@@ -664,12 +628,6 @@
     </r>
   </si>
   <si>
-    <t>Ver hoja RECURSOS de este mismo archivo. Solo llena esta hoja para los recursos donde quieras mostrar su ubicación en un mapa dentro del club (ej. para escanear un QR en el lugar).</t>
-  </si>
-  <si>
-    <t>Coordenada GPS del recurso dentro del club.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -696,9 +654,6 @@
     <t>Formato AAAA-MM-DD HH:MM.</t>
   </si>
   <si>
-    <t>Motivo por el que el recurso no está disponible en ese periodo, ej. 'Mantenimiento'.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -719,24 +674,6 @@
     </r>
   </si>
   <si>
-    <t>Nombre del entrenador.</t>
-  </si>
-  <si>
-    <t>Apellido paterno del entrenador.</t>
-  </si>
-  <si>
-    <t>Apellido materno del entrenador, si aplica.</t>
-  </si>
-  <si>
-    <t>Correo del entrenador, si se tiene.</t>
-  </si>
-  <si>
-    <t>Teléfono del entrenador, si se tiene.</t>
-  </si>
-  <si>
-    <t>Amenidad con la que se asocia principalmente a este entrenador (ver hoja AMENIDADES), si aplica. Opcional.</t>
-  </si>
-  <si>
     <t>Nombre del archivo de fotografía del entrenador, si se tiene.</t>
   </si>
   <si>
@@ -799,9 +736,6 @@
     <t>Ver hoja ENTRENADORES de este mismo archivo.</t>
   </si>
   <si>
-    <t>Ver catálogo ESPECIALIDADES en 01_CATALOGOS. Una fila por cada especialidad que domine el entrenador.</t>
-  </si>
-  <si>
     <t>Tenis</t>
   </si>
   <si>
@@ -828,9 +762,6 @@
     </r>
   </si>
   <si>
-    <t>Nombre del día (Lunes a Domingo). Una fila por cada franja de disponibilidad.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -860,9 +791,6 @@
     <t>Ver hoja RECURSOS de este mismo archivo. Recurso específico donde se imparte la clase.</t>
   </si>
   <si>
-    <t>Nombre del día (Lunes a Domingo). Una fila por cada día que se imparte la clase.</t>
-  </si>
-  <si>
     <t>Cupo máximo de la clase.</t>
   </si>
   <si>
@@ -922,22 +850,112 @@
     <t>Ver hoja HORARIOS DE CLASES de este mismo archivo. Junto con el nombre de la clase identifica el horario exacto en el que está inscrito el socio.</t>
   </si>
   <si>
-    <t>Ver hoja SOCIOS en 03_SOCIOS.</t>
-  </si>
-  <si>
-    <t>Nombre del socio, para referencia visual.</t>
-  </si>
-  <si>
-    <t>Apellido paterno del socio, para referencia visual.</t>
-  </si>
-  <si>
-    <t>Apellido materno del socio, para referencia visual.</t>
-  </si>
-  <si>
     <t>Formato AAAA-MM-DD HH:MM. Si no se conoce, se puede dejar vacía.</t>
   </si>
   <si>
     <t>Formato AAAA-MM-DD HH:MM. Déjala vacía si la inscripción sigue vigente.</t>
+  </si>
+  <si>
+    <t>Ver CLUBES en 02_CLUBES_Y_CONFIGURACION</t>
+  </si>
+  <si>
+    <t>Nombre de la amenidad</t>
+  </si>
+  <si>
+    <t>Descripción breve</t>
+  </si>
+  <si>
+    <t>Una de: Por hora,  Por día, Por capacidad</t>
+  </si>
+  <si>
+    <t>SÍ/NO</t>
+  </si>
+  <si>
+    <t>Ruta de archivo</t>
+  </si>
+  <si>
+    <t>Ruta del archivo</t>
+  </si>
+  <si>
+    <t>Nombre o ruta del archivo</t>
+  </si>
+  <si>
+    <t>Ver catálogo CLUBES en 02_CLUBES_Y_CONFIGURACION</t>
+  </si>
+  <si>
+    <t>Ver hoja AMENIDADES de este mismo archivo</t>
+  </si>
+  <si>
+    <t>Nombre del día  Una fila por cada día que la amenidad esté disponible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de  AMENIDADES </t>
+  </si>
+  <si>
+    <t>Unidad reservable dentro de la amenidad</t>
+  </si>
+  <si>
+    <t>Cupo de este recurso</t>
+  </si>
+  <si>
+    <t>Duración de cada turno reservable</t>
+  </si>
+  <si>
+    <t>Ver hoja RECURSOS de este mismo archivo</t>
+  </si>
+  <si>
+    <t>latituid</t>
+  </si>
+  <si>
+    <t>longitud</t>
+  </si>
+  <si>
+    <t>Motivo por el que el recurso no está disponible en ese periodo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre </t>
+  </si>
+  <si>
+    <t>Apellido paterno</t>
+  </si>
+  <si>
+    <t>Apellido materno</t>
+  </si>
+  <si>
+    <t>Correo del entrenador</t>
+  </si>
+  <si>
+    <t>Teléfono</t>
+  </si>
+  <si>
+    <t>Amenidad con la que se asocia principalmente a este entrenador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ver hoja ENTRENADORES </t>
+  </si>
+  <si>
+    <t>Ver hoja ENTRENADORES</t>
+  </si>
+  <si>
+    <t>Ver catálogo ESPECIALIDADES en 01_CATALOGOS. Una fila por cada especialidad del entrenador</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>paterno</t>
+  </si>
+  <si>
+    <t>materno</t>
+  </si>
+  <si>
+    <t>Nombre del día (Lunes a Domingo). Una fila por cada dia de disponibilidad.</t>
+  </si>
+  <si>
+    <t>Nombre del día Una fila por cada día que se imparte la clase</t>
+  </si>
+  <si>
+    <t>numero</t>
   </si>
 </sst>
 </file>
@@ -948,7 +966,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1014,6 +1032,10 @@
       <i/>
       <sz val="9"/>
       <color rgb="FFB0BEC5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -1136,7 +1158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1187,6 +1209,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1525,22 +1548,21 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.453125" customWidth="1"/>
     <col min="2" max="2" width="38.26953125" customWidth="1"/>
     <col min="3" max="3" width="30.90625" customWidth="1"/>
     <col min="4" max="4" width="29.1796875" customWidth="1"/>
-    <col min="5" max="5" width="33.90625" customWidth="1"/>
-    <col min="6" max="6" width="34.26953125" customWidth="1"/>
-    <col min="7" max="7" width="22.453125" customWidth="1"/>
-    <col min="8" max="8" width="19.453125" customWidth="1"/>
+    <col min="5" max="5" width="34.26953125" customWidth="1"/>
+    <col min="6" max="6" width="22.453125" customWidth="1"/>
+    <col min="7" max="7" width="26.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>217</v>
+    <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>195</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -1548,9 +1570,8 @@
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-    </row>
-    <row r="2" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>20</v>
       </c>
@@ -1564,47 +1585,41 @@
         <v>79</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="H2" s="12" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>133</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>218</v>
+        <v>147</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1612,7 +1627,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.453125" customWidth="1"/>
@@ -1620,18 +1635,17 @@
     <col min="3" max="3" width="25.26953125" customWidth="1"/>
     <col min="4" max="4" width="27.26953125" customWidth="1"/>
     <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="6" max="6" width="23.90625" customWidth="1"/>
     <col min="7" max="8" width="20.81640625" customWidth="1"/>
-    <col min="9" max="9" width="40.453125" customWidth="1"/>
-    <col min="10" max="10" width="33.453125" customWidth="1"/>
-    <col min="11" max="11" width="18.1796875" customWidth="1"/>
-    <col min="12" max="12" width="19.453125" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="9" max="9" width="33.453125" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
+    <col min="11" max="11" width="23.7265625" customWidth="1"/>
+    <col min="12" max="12" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -1644,9 +1658,8 @@
       <c r="J1" s="21"/>
       <c r="K1" s="21"/>
       <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-    </row>
-    <row r="2" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>20</v>
       </c>
@@ -1671,242 +1684,224 @@
       <c r="H2" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I2" s="13" t="s">
-        <v>80</v>
+      <c r="I2" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="M2" s="12" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>133</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>223</v>
+        <v>147</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="M3" s="14" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="C4" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F4" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="G4" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="H4" t="s">
         <v>113</v>
       </c>
       <c r="I4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J4" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="K4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L4" t="s">
         <v>46</v>
       </c>
-      <c r="M4">
+      <c r="L4">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="C5" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F5" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="G5" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="H5" t="s">
         <v>113</v>
       </c>
       <c r="I5" t="s">
+        <v>151</v>
+      </c>
+      <c r="J5" t="s">
+        <v>204</v>
+      </c>
+      <c r="K5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" t="s">
         <v>205</v>
       </c>
-      <c r="J5" t="s">
-        <v>159</v>
-      </c>
-      <c r="K5" t="s">
-        <v>228</v>
-      </c>
-      <c r="L5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B6" t="s">
-        <v>229</v>
-      </c>
       <c r="C6" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="F6" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="G6" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="H6" t="s">
         <v>113</v>
       </c>
       <c r="I6" t="s">
+        <v>148</v>
+      </c>
+      <c r="J6" t="s">
+        <v>207</v>
+      </c>
+      <c r="K6" t="s">
+        <v>208</v>
+      </c>
+      <c r="L6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" t="s">
         <v>205</v>
       </c>
-      <c r="J6" t="s">
-        <v>156</v>
-      </c>
-      <c r="K6" t="s">
-        <v>231</v>
-      </c>
-      <c r="L6" t="s">
-        <v>232</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" t="s">
-        <v>229</v>
-      </c>
       <c r="C7" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="F7" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="G7" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="H7" t="s">
         <v>113</v>
       </c>
       <c r="I7" t="s">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="J7" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="K7" t="s">
-        <v>231</v>
-      </c>
-      <c r="L7" t="s">
-        <v>232</v>
-      </c>
-      <c r="M7">
+        <v>208</v>
+      </c>
+      <c r="L7">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="C8" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E8" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F8" t="s">
         <v>117</v>
@@ -1918,36 +1913,33 @@
         <v>91</v>
       </c>
       <c r="I8" t="s">
+        <v>203</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" t="s">
         <v>207</v>
       </c>
-      <c r="J8" t="s">
-        <v>227</v>
-      </c>
-      <c r="K8" t="s">
-        <v>46</v>
-      </c>
-      <c r="L8" t="s">
-        <v>231</v>
-      </c>
-      <c r="M8">
+      <c r="L8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="C9" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F9" t="s">
         <v>117</v>
@@ -1959,36 +1951,33 @@
         <v>91</v>
       </c>
       <c r="I9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9" t="s">
         <v>207</v>
       </c>
-      <c r="J9" t="s">
-        <v>159</v>
-      </c>
-      <c r="K9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L9" t="s">
-        <v>231</v>
-      </c>
-      <c r="M9">
+      <c r="L9">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B10" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="C10" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E10" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="F10" t="s">
         <v>89</v>
@@ -1997,27 +1986,24 @@
         <v>90</v>
       </c>
       <c r="H10" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="I10" t="s">
-        <v>201</v>
+        <v>154</v>
       </c>
       <c r="J10" t="s">
-        <v>162</v>
+        <v>46</v>
       </c>
       <c r="K10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" t="s">
-        <v>231</v>
-      </c>
-      <c r="M10">
+        <v>207</v>
+      </c>
+      <c r="L10">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2042,7 +2028,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -2091,31 +2077,31 @@
         <v>133</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -3333,17 +3319,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A71:K71"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A64:M64"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A36:D36"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="A43:H43"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A71:K71"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A64:M64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3358,14 +3344,14 @@
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="61.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="5" max="5" width="20.54296875" customWidth="1"/>
     <col min="6" max="6" width="29.90625" customWidth="1"/>
     <col min="7" max="7" width="33.81640625" customWidth="1"/>
     <col min="8" max="8" width="36.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>132</v>
       </c>
       <c r="B1" s="21"/>
@@ -3404,42 +3390,42 @@
     </row>
     <row r="3" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>135</v>
+        <v>218</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>136</v>
+        <v>219</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>137</v>
+        <v>220</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
         <v>57</v>
@@ -3447,16 +3433,16 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C5" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
         <v>57</v>
@@ -3464,16 +3450,16 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E6" t="s">
         <v>57</v>
@@ -3481,16 +3467,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" t="s">
         <v>141</v>
       </c>
-      <c r="B7" t="s">
-        <v>148</v>
-      </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E7" t="s">
         <v>57</v>
@@ -3498,16 +3484,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
         <v>57</v>
@@ -3526,15 +3512,16 @@
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.90625" customWidth="1"/>
     <col min="2" max="2" width="27.26953125" customWidth="1"/>
-    <col min="3" max="4" width="20.81640625" customWidth="1"/>
-    <col min="5" max="5" width="18.1796875" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
+    <col min="4" max="4" width="20.81640625" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -3560,529 +3547,529 @@
     </row>
     <row r="3" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>133</v>
+        <v>224</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>153</v>
+        <v>225</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>154</v>
+        <v>226</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E4" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C6" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E7" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C9" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E10" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E11" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E12" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C13" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E13" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B14" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C14" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D14" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E14" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C15" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C16" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E16" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C17" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D17" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E17" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C18" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D18" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E18" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C19" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E19" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C20" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D20" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E20" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B21" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C21" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E21" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" t="s">
         <v>141</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>148</v>
       </c>
-      <c r="C22" t="s">
-        <v>156</v>
-      </c>
       <c r="D22" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E22" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>134</v>
+      </c>
+      <c r="B23" t="s">
         <v>141</v>
       </c>
-      <c r="B23" t="s">
-        <v>148</v>
-      </c>
       <c r="C23" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E23" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" t="s">
         <v>141</v>
       </c>
-      <c r="B24" t="s">
-        <v>148</v>
-      </c>
       <c r="C24" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D24" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E24" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" t="s">
         <v>141</v>
       </c>
-      <c r="B25" t="s">
-        <v>148</v>
-      </c>
       <c r="C25" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D25" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E25" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" t="s">
         <v>141</v>
       </c>
-      <c r="B26" t="s">
-        <v>148</v>
-      </c>
       <c r="C26" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D26" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E26" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" t="s">
         <v>141</v>
       </c>
-      <c r="B27" t="s">
-        <v>148</v>
-      </c>
       <c r="C27" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E27" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" t="s">
+        <v>148</v>
+      </c>
+      <c r="D28" t="s">
         <v>149</v>
       </c>
-      <c r="C28" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" t="s">
-        <v>157</v>
-      </c>
       <c r="E28" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B29" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D29" t="s">
         <v>149</v>
       </c>
-      <c r="C29" t="s">
-        <v>159</v>
-      </c>
-      <c r="D29" t="s">
-        <v>157</v>
-      </c>
       <c r="E29" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" t="s">
+        <v>152</v>
+      </c>
+      <c r="D30" t="s">
         <v>149</v>
       </c>
-      <c r="C30" t="s">
-        <v>160</v>
-      </c>
-      <c r="D30" t="s">
-        <v>157</v>
-      </c>
       <c r="E30" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" t="s">
         <v>149</v>
       </c>
-      <c r="C31" t="s">
-        <v>161</v>
-      </c>
-      <c r="D31" t="s">
-        <v>157</v>
-      </c>
       <c r="E31" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B32" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" t="s">
         <v>149</v>
       </c>
-      <c r="C32" t="s">
-        <v>162</v>
-      </c>
-      <c r="D32" t="s">
-        <v>157</v>
-      </c>
       <c r="E32" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B33" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" t="s">
+        <v>155</v>
+      </c>
+      <c r="D33" t="s">
         <v>149</v>
       </c>
-      <c r="C33" t="s">
-        <v>163</v>
-      </c>
-      <c r="D33" t="s">
-        <v>157</v>
-      </c>
       <c r="E33" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -4100,15 +4087,15 @@
   <cols>
     <col min="1" max="1" width="19.453125" customWidth="1"/>
     <col min="2" max="2" width="27.26953125" customWidth="1"/>
-    <col min="3" max="3" width="23.36328125" customWidth="1"/>
+    <col min="3" max="3" width="32.54296875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="37.7265625" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>164</v>
+      <c r="A1" s="22" t="s">
+        <v>156</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -4141,30 +4128,30 @@
         <v>133</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>153</v>
+        <v>227</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>166</v>
+        <v>229</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>168</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -4178,13 +4165,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -4198,13 +4185,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -4218,13 +4205,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -4238,13 +4225,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -4258,13 +4245,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F9" t="s">
         <v>57</v>
@@ -4272,13 +4259,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="F10" t="s">
         <v>57</v>
@@ -4286,13 +4273,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F11" t="s">
         <v>57</v>
@@ -4300,13 +4287,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="F12" t="s">
         <v>57</v>
@@ -4314,13 +4301,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -4331,13 +4318,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B14" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C14" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -4348,13 +4335,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C15" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -4365,13 +4352,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C16" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -4382,13 +4369,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C17" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -4399,13 +4386,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C18" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -4416,13 +4403,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C19" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -4433,13 +4420,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C20" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -4453,13 +4440,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B21" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C21" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -4473,13 +4460,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B22" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C22" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -4493,13 +4480,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B23" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C23" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -4513,13 +4500,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" t="s">
         <v>141</v>
       </c>
-      <c r="B24" t="s">
-        <v>148</v>
-      </c>
       <c r="C24" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -4533,13 +4520,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" t="s">
         <v>141</v>
       </c>
-      <c r="B25" t="s">
-        <v>148</v>
-      </c>
       <c r="C25" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -4553,13 +4540,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C26" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D26">
         <v>5</v>
@@ -4593,8 +4580,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>185</v>
+      <c r="A1" s="22" t="s">
+        <v>173</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -4627,19 +4614,19 @@
         <v>133</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>186</v>
+        <v>231</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>187</v>
+        <v>232</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>137</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -4660,12 +4647,12 @@
     <col min="3" max="3" width="36.7265625" customWidth="1"/>
     <col min="4" max="4" width="35.36328125" customWidth="1"/>
     <col min="5" max="5" width="29.90625" customWidth="1"/>
-    <col min="6" max="6" width="23.36328125" customWidth="1"/>
+    <col min="6" max="6" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -4695,22 +4682,22 @@
     </row>
     <row r="3" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>133</v>
+        <v>224</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -4730,14 +4717,14 @@
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="4" width="20.81640625" customWidth="1"/>
     <col min="5" max="5" width="41.26953125" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="40.26953125" customWidth="1"/>
+    <col min="6" max="6" width="27.6328125" customWidth="1"/>
+    <col min="7" max="7" width="49.453125" customWidth="1"/>
     <col min="8" max="8" width="39" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -4778,30 +4765,30 @@
         <v>133</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>193</v>
+        <v>235</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
         <v>89</v>
@@ -4810,38 +4797,38 @@
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="F4" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="C5" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D5" t="s">
         <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="F5" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
         <v>117</v>
@@ -4853,18 +4840,18 @@
         <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="F6" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="C7" t="s">
         <v>86</v>
@@ -4873,10 +4860,10 @@
         <v>119</v>
       </c>
       <c r="E7" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="F7" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -4892,16 +4879,17 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.6328125" customWidth="1"/>
+    <col min="1" max="1" width="37.90625" customWidth="1"/>
     <col min="2" max="2" width="26.08984375" customWidth="1"/>
-    <col min="3" max="4" width="20.81640625" customWidth="1"/>
+    <col min="3" max="3" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="30.81640625" customWidth="1"/>
     <col min="5" max="5" width="47.81640625" customWidth="1"/>
-    <col min="6" max="6" width="32.453125" customWidth="1"/>
+    <col min="6" max="6" width="60.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -4934,24 +4922,24 @@
         <v>133</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>214</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
         <v>89</v>
@@ -4960,18 +4948,18 @@
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="F4" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
         <v>89</v>
@@ -4980,38 +4968,38 @@
         <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="E5" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="F5" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="C6" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D6" t="s">
         <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="F6" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
         <v>117</v>
@@ -5023,18 +5011,18 @@
         <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="F7" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="C8" t="s">
         <v>86</v>
@@ -5043,18 +5031,18 @@
         <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="F8" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="C9" t="s">
         <v>86</v>
@@ -5063,10 +5051,10 @@
         <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="F9" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
